--- a/docs/data/returnees.xlsx
+++ b/docs/data/returnees.xlsx
@@ -92,7 +92,7 @@
     <row r="2">
       <c r="A2" t="inlineStr" s="2">
         <is>
-          <t>Datenstand: 2026-10-05T04:55:57.647093+00:00</t>
+          <t>Datenstand: 2026-10-05T09:08:58.053728+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/data/returnees.xlsx
+++ b/docs/data/returnees.xlsx
@@ -92,7 +92,7 @@
     <row r="2">
       <c r="A2" t="inlineStr" s="2">
         <is>
-          <t>Datenstand: 2026-10-05T09:08:58.053728+00:00</t>
+          <t>Datenstand: 2026-10-05T09:18:47.158566+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/data/returnees.xlsx
+++ b/docs/data/returnees.xlsx
@@ -92,7 +92,7 @@
     <row r="2">
       <c r="A2" t="inlineStr" s="2">
         <is>
-          <t>Datenstand: 2026-10-05T09:18:47.158566+00:00</t>
+          <t>Datenstand: 2026-10-05T09:28:35.280761+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/data/returnees.xlsx
+++ b/docs/data/returnees.xlsx
@@ -92,7 +92,7 @@
     <row r="2">
       <c r="A2" t="inlineStr" s="2">
         <is>
-          <t>Datenstand: 2026-10-05T09:28:35.280761+00:00</t>
+          <t>Datenstand: 2026-10-05T09:38:25.425412+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/data/returnees.xlsx
+++ b/docs/data/returnees.xlsx
@@ -92,7 +92,7 @@
     <row r="2">
       <c r="A2" t="inlineStr" s="2">
         <is>
-          <t>Datenstand: 2026-10-05T09:38:25.425412+00:00</t>
+          <t>Datenstand: 2026-10-05T09:48:12.528349+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/data/returnees.xlsx
+++ b/docs/data/returnees.xlsx
@@ -92,7 +92,7 @@
     <row r="2">
       <c r="A2" t="inlineStr" s="2">
         <is>
-          <t>Datenstand: 2026-10-05T09:48:12.528349+00:00</t>
+          <t>Datenstand: 2026-10-05T09:57:59.199229+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/data/returnees.xlsx
+++ b/docs/data/returnees.xlsx
@@ -92,7 +92,7 @@
     <row r="2">
       <c r="A2" t="inlineStr" s="2">
         <is>
-          <t>Datenstand: 2026-10-05T09:57:59.199229+00:00</t>
+          <t>Datenstand: 2026-10-05T10:08:03.433845+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/data/returnees.xlsx
+++ b/docs/data/returnees.xlsx
@@ -92,7 +92,7 @@
     <row r="2">
       <c r="A2" t="inlineStr" s="2">
         <is>
-          <t>Datenstand: 2026-10-05T04:55:57.647093+00:00</t>
+          <t>Datenstand: 2026-10-05T10:19:03.155776+00:00</t>
         </is>
       </c>
     </row>
